--- a/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_BS MAT ANUAL MATRIZ TUTOR.xlsx
+++ b/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_BS MAT ANUAL MATRIZ TUTOR.xlsx
@@ -59,7 +59,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd.mm"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -246,7 +246,17 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00065F46"/>
     </font>
   </fonts>
   <fills count="33">
@@ -426,24 +436,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="60">
     <border/>
     <border>
       <left style="hair">
@@ -988,11 +998,16 @@
         <color rgb="FF104861"/>
       </top>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1859,19 +1874,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2177,6 +2199,12 @@
       <text>
         <t>Sistema: 9.30
 Diferencia: 0.04</t>
+      </text>
+    </comment>
+    <comment ref="N40" authorId="0" shapeId="0">
+      <text>
+        <t>Sistema: 7.96
+Diferencia: 0.07</t>
       </text>
     </comment>
     <comment ref="N41" authorId="0" shapeId="0">
@@ -2503,13 +2531,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" style="254" min="1" max="1"/>
-    <col width="40" customWidth="1" style="254" min="2" max="2"/>
-    <col width="25" customWidth="1" style="254" min="3" max="3"/>
-    <col width="60" customWidth="1" style="254" min="4" max="4"/>
+    <col width="35" customWidth="1" style="254" min="1" max="1"/>
+    <col width="25" customWidth="1" style="254" min="2" max="2"/>
+    <col width="30" customWidth="1" style="254" min="3" max="3"/>
+    <col width="12" customWidth="1" style="254" min="4" max="4"/>
+    <col width="12" customWidth="1" style="254" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="254">
@@ -2521,1858 +2550,1181 @@
       <c r="B1" s="294" t="n"/>
       <c r="C1" s="294" t="n"/>
       <c r="D1" s="294" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="254">
-      <c r="A2" s="295" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="295" t="inlineStr">
+      <c r="E1" s="294" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="254">
+      <c r="A3" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 10AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="254">
+      <c r="A4" s="296" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="295" t="inlineStr">
+      <c r="B4" s="296" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="295" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1" s="254">
-      <c r="A3" s="296" t="inlineStr">
-        <is>
-          <t>10AM</t>
-        </is>
-      </c>
-      <c r="B3" s="297" t="inlineStr">
+      <c r="C4" s="296" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="296" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="296" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="254">
+      <c r="A5" s="297" t="inlineStr">
         <is>
           <t>BARROS VELESACA EMILIO NICOLAS</t>
         </is>
       </c>
-      <c r="C3" s="296" t="inlineStr">
+      <c r="B5" s="297" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D3" s="297" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 8.39 vs Sistema: 8.77)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" s="254">
-      <c r="A4" s="298" t="inlineStr">
-        <is>
-          <t>10AM</t>
-        </is>
-      </c>
-      <c r="B4" s="299" t="inlineStr">
-        <is>
-          <t>BARROS VELESACA EMILIO NICOLAS</t>
-        </is>
-      </c>
-      <c r="C4" s="298" t="inlineStr">
+      <c r="C5" s="298" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D5" s="297" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E5" s="297" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="254">
+      <c r="A6" s="299" t="n"/>
+      <c r="B6" s="299" t="n"/>
+      <c r="C6" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D6" s="301" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E6" s="301" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="254">
+      <c r="A8" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 10BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="254">
+      <c r="A9" s="296" t="inlineStr">
+        <is>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="B9" s="296" t="inlineStr">
+        <is>
+          <t>Tipo de Problema</t>
+        </is>
+      </c>
+      <c r="C9" s="296" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D9" s="296" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E9" s="296" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="254">
+      <c r="A10" s="301" t="inlineStr">
+        <is>
+          <t>APOLO GUZMAN ANTHONY IVAN</t>
+        </is>
+      </c>
+      <c r="B10" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D4" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.97 vs Sistema: 8.03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" s="254">
-      <c r="A5" s="296" t="inlineStr">
-        <is>
-          <t>10BM</t>
-        </is>
-      </c>
-      <c r="B5" s="297" t="inlineStr">
-        <is>
-          <t>APOLO GUZMAN ANTHONY IVAN</t>
-        </is>
-      </c>
-      <c r="C5" s="296" t="inlineStr">
+      <c r="C10" s="300" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D10" s="301" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="E10" s="301" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="254">
+      <c r="A12" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 8AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" s="254">
+      <c r="A13" s="302" t="inlineStr">
+        <is>
+          <t>✅ Todo el curso está perfectamente cuadrado. No hay discrepancias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="254">
+      <c r="A15" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 8BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="254">
+      <c r="A16" s="296" t="inlineStr">
+        <is>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="B16" s="296" t="inlineStr">
+        <is>
+          <t>Tipo de Problema</t>
+        </is>
+      </c>
+      <c r="C16" s="296" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D16" s="296" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E16" s="296" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="254">
+      <c r="A17" s="301" t="inlineStr">
+        <is>
+          <t>ARIAS CUZCO JOSUE DAVID</t>
+        </is>
+      </c>
+      <c r="B17" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D5" s="297" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 9.67 vs Sistema: 9.75)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" s="254">
-      <c r="A6" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B6" s="299" t="inlineStr">
-        <is>
-          <t>ARIAS CUZCO JOSUE DAVID</t>
-        </is>
-      </c>
-      <c r="C6" s="298" t="inlineStr">
+      <c r="C17" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D17" s="301" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E17" s="301" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="254">
+      <c r="A18" s="301" t="inlineStr">
+        <is>
+          <t>ATANCURI LALVAY JOEL MATIAS</t>
+        </is>
+      </c>
+      <c r="B18" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D6" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.36 vs Sistema: 8.44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1" s="254">
-      <c r="A7" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B7" s="297" t="inlineStr">
-        <is>
-          <t>ATANCURI LALVAY JOEL MATIAS</t>
-        </is>
-      </c>
-      <c r="C7" s="296" t="inlineStr">
+      <c r="C18" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D18" s="301" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E18" s="301" t="n">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="254">
+      <c r="A19" s="301" t="inlineStr">
+        <is>
+          <t>BARBECHO TELLO EMILY BRIGITTE</t>
+        </is>
+      </c>
+      <c r="B19" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D7" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.8 vs Sistema: 8.84)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1" s="254">
-      <c r="A8" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B8" s="299" t="inlineStr">
-        <is>
-          <t>BARBECHO TELLO EMILY BRIGITTE</t>
-        </is>
-      </c>
-      <c r="C8" s="298" t="inlineStr">
+      <c r="C19" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D19" s="301" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E19" s="301" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="254">
+      <c r="A20" s="301" t="inlineStr">
+        <is>
+          <t>BELTRAN CARDENAS CRISTEL ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="B20" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D8" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.5 vs Sistema: 9.56)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" s="254">
-      <c r="A9" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B9" s="297" t="inlineStr">
-        <is>
-          <t>BELTRAN CARDENAS CRISTEL ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="C9" s="296" t="inlineStr">
+      <c r="C20" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D20" s="301" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="E20" s="301" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="254">
+      <c r="A21" s="301" t="inlineStr">
+        <is>
+          <t>CHIMBOLEMA AREVALO WILLIAM ELIAS</t>
+        </is>
+      </c>
+      <c r="B21" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D9" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.32 vs Sistema: 9.38)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" s="254">
-      <c r="A10" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B10" s="299" t="inlineStr">
-        <is>
-          <t>CHIMBOLEMA AREVALO WILLIAM ELIAS</t>
-        </is>
-      </c>
-      <c r="C10" s="298" t="inlineStr">
+      <c r="C21" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D21" s="301" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E21" s="301" t="n">
+        <v>8.710000000000001</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="254">
+      <c r="A22" s="301" t="inlineStr">
+        <is>
+          <t>CRESPO BARROS DAVID SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="B22" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D10" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.66 vs Sistema: 8.71)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1" s="254">
-      <c r="A11" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B11" s="297" t="inlineStr">
-        <is>
-          <t>CRESPO BARROS DAVID SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C11" s="296" t="inlineStr">
+      <c r="C22" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D22" s="301" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="E22" s="301" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="254">
+      <c r="A23" s="301" t="inlineStr">
+        <is>
+          <t>FARFAN ALVARADO MAYKEL YAHIR</t>
+        </is>
+      </c>
+      <c r="B23" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D11" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.19 vs Sistema: 8.26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1" s="254">
-      <c r="A12" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B12" s="299" t="inlineStr">
-        <is>
-          <t>FARFAN ALVARADO MAYKEL YAHIR</t>
-        </is>
-      </c>
-      <c r="C12" s="298" t="inlineStr">
+      <c r="C23" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D23" s="301" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E23" s="301" t="n">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="254">
+      <c r="A24" s="301" t="inlineStr">
+        <is>
+          <t>GUALLPA JARA NATHALY GABRIELA</t>
+        </is>
+      </c>
+      <c r="B24" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D12" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.05 vs Sistema: 9.11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1" s="254">
-      <c r="A13" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B13" s="297" t="inlineStr">
-        <is>
-          <t>GUALLPA JARA NATHALY GABRIELA</t>
-        </is>
-      </c>
-      <c r="C13" s="296" t="inlineStr">
+      <c r="C24" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D24" s="301" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="E24" s="301" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="254">
+      <c r="A25" s="301" t="inlineStr">
+        <is>
+          <t>JUELA GOMEZ DOMENICA VALENTINA</t>
+        </is>
+      </c>
+      <c r="B25" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D13" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.02 vs Sistema: 8.06)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" s="254">
-      <c r="A14" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B14" s="299" t="inlineStr">
-        <is>
-          <t>JUELA GOMEZ DOMENICA VALENTINA</t>
-        </is>
-      </c>
-      <c r="C14" s="298" t="inlineStr">
+      <c r="C25" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D25" s="301" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="E25" s="301" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="254">
+      <c r="A26" s="297" t="inlineStr">
+        <is>
+          <t>LONDA ASMAL ANDERSON JULIAN</t>
+        </is>
+      </c>
+      <c r="B26" s="297" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D14" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.94 vs Sistema: 9.03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1" s="254">
-      <c r="A15" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B15" s="297" t="inlineStr">
-        <is>
-          <t>LONDA ASMAL ANDERSON JULIAN</t>
-        </is>
-      </c>
-      <c r="C15" s="296" t="inlineStr">
+      <c r="C26" s="298" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D26" s="297" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="E26" s="297" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="254">
+      <c r="A27" s="299" t="n"/>
+      <c r="B27" s="299" t="n"/>
+      <c r="C27" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D27" s="301" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="E27" s="301" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="254">
+      <c r="A28" s="301" t="inlineStr">
+        <is>
+          <t>LONDA PASTUIZACA ANTONY MATEO</t>
+        </is>
+      </c>
+      <c r="B28" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D15" s="297" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 7.57 vs Sistema: 7.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1" s="254">
-      <c r="A16" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B16" s="299" t="inlineStr">
-        <is>
-          <t>LONDA ASMAL ANDERSON JULIAN</t>
-        </is>
-      </c>
-      <c r="C16" s="298" t="inlineStr">
+      <c r="C28" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D28" s="301" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="E28" s="301" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="254">
+      <c r="A29" s="301" t="inlineStr">
+        <is>
+          <t>MAYORGA JIMBO CHRISTOFER STALIN</t>
+        </is>
+      </c>
+      <c r="B29" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D16" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.24 vs Sistema: 7.34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1" s="254">
-      <c r="A17" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B17" s="297" t="inlineStr">
-        <is>
-          <t>LONDA PASTUIZACA ANTONY MATEO</t>
-        </is>
-      </c>
-      <c r="C17" s="296" t="inlineStr">
+      <c r="C29" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D29" s="301" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="E29" s="301" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="254">
+      <c r="A30" s="301" t="inlineStr">
+        <is>
+          <t>MOROCHO HERNANDEZ KIMBERLY IVANA</t>
+        </is>
+      </c>
+      <c r="B30" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D17" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.02 vs Sistema: 8.17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1" s="254">
-      <c r="A18" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B18" s="299" t="inlineStr">
-        <is>
-          <t>MAYORGA JIMBO CHRISTOFER STALIN</t>
-        </is>
-      </c>
-      <c r="C18" s="298" t="inlineStr">
+      <c r="C30" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D30" s="301" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="E30" s="301" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="254">
+      <c r="A31" s="297" t="inlineStr">
+        <is>
+          <t>NACIPUCHA NACIPUCHA EDWIN ANDRES</t>
+        </is>
+      </c>
+      <c r="B31" s="297" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D18" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.37 vs Sistema: 7.34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1" s="254">
-      <c r="A19" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B19" s="297" t="inlineStr">
-        <is>
-          <t>MOROCHO HERNANDEZ KIMBERLY IVANA</t>
-        </is>
-      </c>
-      <c r="C19" s="296" t="inlineStr">
+      <c r="C31" s="298" t="inlineStr">
+        <is>
+          <t>Estudios Sociales</t>
+        </is>
+      </c>
+      <c r="D31" s="297" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E31" s="297" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="254">
+      <c r="A32" s="299" t="n"/>
+      <c r="B32" s="299" t="n"/>
+      <c r="C32" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D32" s="301" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E32" s="301" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="254">
+      <c r="A33" s="297" t="inlineStr">
+        <is>
+          <t>PERALTA PUCHA JORDAN EDUARDO</t>
+        </is>
+      </c>
+      <c r="B33" s="297" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D19" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.87 vs Sistema: 7.94)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" s="254">
-      <c r="A20" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B20" s="299" t="inlineStr">
-        <is>
-          <t>NACIPUCHA NACIPUCHA EDWIN ANDRES</t>
-        </is>
-      </c>
-      <c r="C20" s="298" t="inlineStr">
+      <c r="C33" s="298" t="inlineStr">
+        <is>
+          <t>Estudios Sociales</t>
+        </is>
+      </c>
+      <c r="D33" s="297" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="E33" s="297" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="254">
+      <c r="C34" s="298" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D34" s="297" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E34" s="297" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="254">
+      <c r="C35" s="298" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D35" s="297" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E35" s="297" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="254">
+      <c r="A36" s="299" t="n"/>
+      <c r="B36" s="299" t="n"/>
+      <c r="C36" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D36" s="301" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E36" s="301" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="254">
+      <c r="A37" s="301" t="inlineStr">
+        <is>
+          <t>PIÑA LLANGARI NICOLE DOMENICA</t>
+        </is>
+      </c>
+      <c r="B37" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D20" s="299" t="inlineStr">
-        <is>
-          <t>Estudios Sociales (Docente: 8.15 vs Sistema: 8.12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" s="254">
-      <c r="A21" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B21" s="297" t="inlineStr">
-        <is>
-          <t>NACIPUCHA NACIPUCHA EDWIN ANDRES</t>
-        </is>
-      </c>
-      <c r="C21" s="296" t="inlineStr">
+      <c r="C37" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D37" s="301" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E37" s="301" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="254">
+      <c r="A38" s="301" t="inlineStr">
+        <is>
+          <t>QUINDE ZUMBA DANIEL ANDRES</t>
+        </is>
+      </c>
+      <c r="B38" s="301" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D21" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.64 vs Sistema: 8.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" s="254">
-      <c r="A22" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B22" s="299" t="inlineStr">
-        <is>
-          <t>NIVICELA ESPINOZA JOSCAR AARON</t>
-        </is>
-      </c>
-      <c r="C22" s="298" t="inlineStr">
+      <c r="C38" s="300" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D38" s="301" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="301" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="254">
+      <c r="A39" s="301" t="inlineStr">
+        <is>
+          <t>SONGOR MUZHA ASHLEY NICOLE</t>
+        </is>
+      </c>
+      <c r="B39" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C39" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D39" s="301" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E39" s="301" t="n">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="254">
+      <c r="A40" s="301" t="inlineStr">
+        <is>
+          <t>SUCUZHAÑAY FERNANDEZ JENNIFER MISHELL</t>
+        </is>
+      </c>
+      <c r="B40" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C40" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D40" s="301" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="E40" s="301" t="n">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="254">
+      <c r="A41" s="297" t="inlineStr">
+        <is>
+          <t>SUIN PERALTA DIEGO EMILIO</t>
+        </is>
+      </c>
+      <c r="B41" s="297" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C41" s="298" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D41" s="297" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E41" s="297" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" s="254">
+      <c r="A42" s="299" t="n"/>
+      <c r="B42" s="299" t="n"/>
+      <c r="C42" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D42" s="301" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E42" s="301" t="n">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="254">
+      <c r="A43" s="301" t="inlineStr">
+        <is>
+          <t>TACURI NAVARRO AMANDA PAOLA</t>
+        </is>
+      </c>
+      <c r="B43" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C43" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D43" s="301" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E43" s="301" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="254">
+      <c r="A44" s="297" t="inlineStr">
+        <is>
+          <t>TACURI PINTADO RIHANNA TIFFANNY</t>
+        </is>
+      </c>
+      <c r="B44" s="297" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C44" s="298" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D44" s="297" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="E44" s="297" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" s="254">
+      <c r="C45" s="298" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D45" s="297" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E45" s="297" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" s="254">
+      <c r="A46" s="299" t="n"/>
+      <c r="B46" s="299" t="n"/>
+      <c r="C46" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D46" s="301" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E46" s="301" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="254">
+      <c r="A47" s="301" t="inlineStr">
+        <is>
+          <t>TENEMAZA LEMA VERONICA LIZBETH</t>
+        </is>
+      </c>
+      <c r="B47" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C47" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D47" s="301" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E47" s="301" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" s="254">
+      <c r="A48" s="301" t="inlineStr">
+        <is>
+          <t>TOCTE CORRALES SHIRLE LISETH</t>
+        </is>
+      </c>
+      <c r="B48" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C48" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D48" s="301" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="E48" s="301" t="n">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="254">
+      <c r="A49" s="301" t="inlineStr">
+        <is>
+          <t>UZHCA BANEGAS DANIELA ESTEFANIA</t>
+        </is>
+      </c>
+      <c r="B49" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C49" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D49" s="301" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E49" s="301" t="n">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" s="254">
+      <c r="A50" s="301" t="inlineStr">
+        <is>
+          <t>ZHANGALLIMBAY VEGA KAREN DOMENICA</t>
+        </is>
+      </c>
+      <c r="B50" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C50" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D50" s="301" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="E50" s="301" t="n">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" s="254">
+      <c r="A52" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 9AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" s="254">
+      <c r="A53" s="296" t="inlineStr">
+        <is>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="B53" s="296" t="inlineStr">
+        <is>
+          <t>Tipo de Problema</t>
+        </is>
+      </c>
+      <c r="C53" s="296" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D53" s="296" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E53" s="296" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" s="254">
+      <c r="A54" s="301" t="inlineStr">
+        <is>
+          <t>LOPEZ DELGADO DANNY LEONEL</t>
+        </is>
+      </c>
+      <c r="B54" s="301" t="inlineStr">
+        <is>
+          <t>⚠️ FALTA EN SISTEMA</t>
+        </is>
+      </c>
+      <c r="C54" s="300" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D54" s="301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="301" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="254">
+      <c r="A55" s="301" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO NAVARRO DARWIN ADRIAN</t>
+        </is>
+      </c>
+      <c r="B55" s="301" t="inlineStr">
         <is>
           <t>⚠️ FALTA EN DOCENTE</t>
         </is>
       </c>
-      <c r="D22" s="299" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" s="254">
-      <c r="A23" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B23" s="297" t="inlineStr">
-        <is>
-          <t>NIVICELA ESPINOZA OSCAR AARON</t>
-        </is>
-      </c>
-      <c r="C23" s="296" t="inlineStr">
+      <c r="C55" s="300" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D55" s="301" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="E55" s="301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" s="254">
+      <c r="A57" s="295" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 9BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" s="254">
+      <c r="A58" s="296" t="inlineStr">
+        <is>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="B58" s="296" t="inlineStr">
+        <is>
+          <t>Tipo de Problema</t>
+        </is>
+      </c>
+      <c r="C58" s="296" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D58" s="296" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E58" s="296" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" s="254">
+      <c r="A59" s="297" t="inlineStr">
+        <is>
+          <t>CABRERA CANDO LIZBETH CAROLINA</t>
+        </is>
+      </c>
+      <c r="B59" s="297" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C59" s="298" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D59" s="297" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E59" s="297" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" s="254">
+      <c r="A60" s="299" t="n"/>
+      <c r="B60" s="299" t="n"/>
+      <c r="C60" s="300" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D60" s="301" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E60" s="301" t="n">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" s="254">
+      <c r="A61" s="301" t="inlineStr">
+        <is>
+          <t>LONDA VIÑANZACA NATHALY DANIELA</t>
+        </is>
+      </c>
+      <c r="B61" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C61" s="300" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D61" s="301" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="E61" s="301" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" s="254">
+      <c r="A62" s="301" t="inlineStr">
+        <is>
+          <t>LOPEZ DELGADO DANNY LEONEL</t>
+        </is>
+      </c>
+      <c r="B62" s="301" t="inlineStr">
+        <is>
+          <t>⚠️ FALTA EN DOCENTE</t>
+        </is>
+      </c>
+      <c r="C62" s="300" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D62" s="301" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="E62" s="301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" s="254">
+      <c r="A63" s="301" t="inlineStr">
+        <is>
+          <t>SOLIZ GUZHÑAY MATEO ISMAEL</t>
+        </is>
+      </c>
+      <c r="B63" s="301" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C63" s="300" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D63" s="301" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E63" s="301" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" s="254">
+      <c r="A64" s="301" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO NAVARRO DARWIN ADRIAN</t>
+        </is>
+      </c>
+      <c r="B64" s="301" t="inlineStr">
         <is>
           <t>⚠️ FALTA EN SISTEMA</t>
         </is>
       </c>
-      <c r="D23" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1" s="254">
-      <c r="A24" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B24" s="299" t="inlineStr">
-        <is>
-          <t>PERALTA PUCHA JORDAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="C24" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D24" s="299" t="inlineStr">
-        <is>
-          <t>Estudios Sociales (Docente: 3.68 vs Sistema: 4.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1" s="254">
-      <c r="A25" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B25" s="297" t="inlineStr">
-        <is>
-          <t>PERALTA PUCHA JORDAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="C25" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D25" s="297" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 4.75 vs Sistema: 3.48)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1" s="254">
-      <c r="A26" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B26" s="299" t="inlineStr">
-        <is>
-          <t>PERALTA PUCHA JORDAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="C26" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D26" s="299" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 4.5 vs Sistema: 4.83)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25" customHeight="1" s="254">
-      <c r="A27" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B27" s="297" t="inlineStr">
-        <is>
-          <t>PERALTA PUCHA JORDAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="C27" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D27" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 4.68 vs Sistema: 4.59)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25" customHeight="1" s="254">
-      <c r="A28" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B28" s="299" t="inlineStr">
-        <is>
-          <t>PIÑA LLANGARI NICOLE DOMENICA</t>
-        </is>
-      </c>
-      <c r="C28" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D28" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.26 vs Sistema: 8.32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="25" customHeight="1" s="254">
-      <c r="A29" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B29" s="297" t="inlineStr">
-        <is>
-          <t>QUINDE ZUMBA DANIEL ANDRES</t>
-        </is>
-      </c>
-      <c r="C29" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D29" s="297" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 10.0 vs Sistema: 9.91)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="25" customHeight="1" s="254">
-      <c r="A30" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B30" s="299" t="inlineStr">
-        <is>
-          <t>SONGOR MUZHA ASHLEY NICOLE</t>
-        </is>
-      </c>
-      <c r="C30" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D30" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.26 vs Sistema: 8.36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="25" customHeight="1" s="254">
-      <c r="A31" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B31" s="297" t="inlineStr">
-        <is>
-          <t>SUCUZHAÑAY FERNANDEZ JENNIFER MISHELL</t>
-        </is>
-      </c>
-      <c r="C31" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D31" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.71 vs Sistema: 9.74)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="25" customHeight="1" s="254">
-      <c r="A32" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B32" s="299" t="inlineStr">
-        <is>
-          <t>SUIN PERALTA DIEGO EMILIO</t>
-        </is>
-      </c>
-      <c r="C32" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D32" s="299" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 7.77 vs Sistema: 7.69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="25" customHeight="1" s="254">
-      <c r="A33" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B33" s="297" t="inlineStr">
-        <is>
-          <t>SUIN PERALTA DIEGO EMILIO</t>
-        </is>
-      </c>
-      <c r="C33" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D33" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.43 vs Sistema: 7.46)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25" customHeight="1" s="254">
-      <c r="A34" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B34" s="299" t="inlineStr">
-        <is>
-          <t>TACURI NAVARRO AMANDA PAOLA</t>
-        </is>
-      </c>
-      <c r="C34" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D34" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.97 vs Sistema: 8.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25" customHeight="1" s="254">
-      <c r="A35" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B35" s="297" t="inlineStr">
-        <is>
-          <t>TACURI PINTADO RIHANNA TIFFANNY</t>
-        </is>
-      </c>
-      <c r="C35" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D35" s="297" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 6.92 vs Sistema: 7.39)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25" customHeight="1" s="254">
-      <c r="A36" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B36" s="299" t="inlineStr">
-        <is>
-          <t>TACURI PINTADO RIHANNA TIFFANNY</t>
-        </is>
-      </c>
-      <c r="C36" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D36" s="299" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 7.47 vs Sistema: 7.39)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25" customHeight="1" s="254">
-      <c r="A37" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B37" s="297" t="inlineStr">
-        <is>
-          <t>TACURI PINTADO RIHANNA TIFFANNY</t>
-        </is>
-      </c>
-      <c r="C37" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D37" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 6.57 vs Sistema: 5.57)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="25" customHeight="1" s="254">
-      <c r="A38" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B38" s="299" t="inlineStr">
-        <is>
-          <t>TENEMAZA LEMA VERONICA LIZBETH</t>
-        </is>
-      </c>
-      <c r="C38" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D38" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.26 vs Sistema: 9.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25" customHeight="1" s="254">
-      <c r="A39" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B39" s="297" t="inlineStr">
-        <is>
-          <t>TOCTE CORRALES SHIRLE LISETH</t>
-        </is>
-      </c>
-      <c r="C39" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D39" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="25" customHeight="1" s="254">
-      <c r="A40" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B40" s="299" t="inlineStr">
-        <is>
-          <t>TOCTE CORRALES SHYRLE LISETH</t>
-        </is>
-      </c>
-      <c r="C40" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D40" s="299" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="25" customHeight="1" s="254">
-      <c r="A41" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B41" s="297" t="inlineStr">
-        <is>
-          <t>UZHCA BANEGAS DANIELA ESTEFANIA</t>
-        </is>
-      </c>
-      <c r="C41" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D41" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 9.5 vs Sistema: 9.55)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="25" customHeight="1" s="254">
-      <c r="A42" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B42" s="299" t="inlineStr">
-        <is>
-          <t>VIZHÑAY MUÑOZ BRAYAN DAMIAN</t>
-        </is>
-      </c>
-      <c r="C42" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D42" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="25" customHeight="1" s="254">
-      <c r="A43" s="296" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B43" s="297" t="inlineStr">
-        <is>
-          <t>VIÑANZACA GUAMÁN ELIAN JOEL</t>
-        </is>
-      </c>
-      <c r="C43" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D43" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="25" customHeight="1" s="254">
-      <c r="A44" s="298" t="inlineStr">
-        <is>
-          <t>8BM</t>
-        </is>
-      </c>
-      <c r="B44" s="299" t="inlineStr">
-        <is>
-          <t>ZHANGALLIMBAY VEGA KAREN DOMENICA</t>
-        </is>
-      </c>
-      <c r="C44" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D44" s="299" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.27 vs Sistema: 8.35)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="25" customHeight="1" s="254">
-      <c r="A45" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B45" s="297" t="inlineStr">
-        <is>
-          <t>AGUDELO ARTAHOMA ISAAC ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C45" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D45" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="25" customHeight="1" s="254">
-      <c r="A46" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B46" s="299" t="inlineStr">
-        <is>
-          <t>AGUDELO ARTAHONA ISAAC ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C46" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D46" s="299" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="25" customHeight="1" s="254">
-      <c r="A47" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B47" s="297" t="inlineStr">
-        <is>
-          <t>BELDUMA BELDUMA MAYETSSI</t>
-        </is>
-      </c>
-      <c r="C47" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D47" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="25" customHeight="1" s="254">
-      <c r="A48" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B48" s="299" t="inlineStr">
-        <is>
-          <t>BELDUMA BELDUMA MAYETSSI YULEYMY</t>
-        </is>
-      </c>
-      <c r="C48" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D48" s="299" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="25" customHeight="1" s="254">
-      <c r="A49" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B49" s="297" t="inlineStr">
-        <is>
-          <t>CHUVA LLANOS RONALD ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C49" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D49" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="25" customHeight="1" s="254">
-      <c r="A50" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B50" s="299" t="inlineStr">
-        <is>
-          <t>CHUÑIR NAREA LUYZIANA VICTORIA</t>
-        </is>
-      </c>
-      <c r="C50" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D50" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="25" customHeight="1" s="254">
-      <c r="A51" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B51" s="297" t="inlineStr">
-        <is>
-          <t>LOPEZ DELGADO DANNY LEONEL</t>
-        </is>
-      </c>
-      <c r="C51" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D51" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="25" customHeight="1" s="254">
-      <c r="A52" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B52" s="299" t="inlineStr">
-        <is>
-          <t>OLAYA GRANDA MIGUEL ANGEL</t>
-        </is>
-      </c>
-      <c r="C52" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D52" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="25" customHeight="1" s="254">
-      <c r="A53" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B53" s="297" t="inlineStr">
-        <is>
-          <t>OLAYA PINTADO AMBAR DANELLE</t>
-        </is>
-      </c>
-      <c r="C53" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D53" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="25" customHeight="1" s="254">
-      <c r="A54" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B54" s="299" t="inlineStr">
-        <is>
-          <t>PEÑAFIEL VELECELA NATALY PAMELA</t>
-        </is>
-      </c>
-      <c r="C54" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D54" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="25" customHeight="1" s="254">
-      <c r="A55" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B55" s="297" t="inlineStr">
-        <is>
-          <t>PIÑA BONETE BRYAN ISMAEL</t>
-        </is>
-      </c>
-      <c r="C55" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D55" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="25" customHeight="1" s="254">
-      <c r="A56" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B56" s="299" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ SARMIENTO TATIANA JHOMAYRA</t>
-        </is>
-      </c>
-      <c r="C56" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D56" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="25" customHeight="1" s="254">
-      <c r="A57" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B57" s="297" t="inlineStr">
-        <is>
-          <t>SIMBAÑA CABRERA BIANCA ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="C57" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D57" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="25" customHeight="1" s="254">
-      <c r="A58" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B58" s="299" t="inlineStr">
-        <is>
-          <t>SINCHI GARCIA ALEXIS JOEL</t>
-        </is>
-      </c>
-      <c r="C58" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D58" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="25" customHeight="1" s="254">
-      <c r="A59" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B59" s="297" t="inlineStr">
-        <is>
-          <t>TAMAYO SIAVICHAY EMILY ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="C59" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D59" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="25" customHeight="1" s="254">
-      <c r="A60" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B60" s="299" t="inlineStr">
-        <is>
-          <t>TORRES LATA ADRIANA JAZU</t>
-        </is>
-      </c>
-      <c r="C60" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D60" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="25" customHeight="1" s="254">
-      <c r="A61" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B61" s="297" t="inlineStr">
-        <is>
-          <t>VACA GONZALEZ PAUL GEOVANNY</t>
-        </is>
-      </c>
-      <c r="C61" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D61" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="25" customHeight="1" s="254">
-      <c r="A62" s="298" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B62" s="299" t="inlineStr">
-        <is>
-          <t>VASQUEZ YUNGA JHOSUE DAMIAN</t>
-        </is>
-      </c>
-      <c r="C62" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D62" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="25" customHeight="1" s="254">
-      <c r="A63" s="296" t="inlineStr">
-        <is>
-          <t>9AM</t>
-        </is>
-      </c>
-      <c r="B63" s="297" t="inlineStr">
-        <is>
-          <t>VILLAVICENCIO NAVARRO DARWIN ADRIAN</t>
-        </is>
-      </c>
-      <c r="C63" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D63" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="25" customHeight="1" s="254">
-      <c r="A64" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B64" s="299" t="inlineStr">
-        <is>
-          <t>CABRERA CANDO LIZBETH CAROLINA</t>
-        </is>
-      </c>
-      <c r="C64" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D64" s="299" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 8.43 vs Sistema: 8.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="25" customHeight="1" s="254">
-      <c r="A65" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B65" s="297" t="inlineStr">
-        <is>
-          <t>CABRERA CANDO LIZBETH CAROLINA</t>
-        </is>
-      </c>
-      <c r="C65" s="296" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D65" s="297" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 7.5 vs Sistema: 7.54)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="25" customHeight="1" s="254">
-      <c r="A66" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B66" s="299" t="inlineStr">
-        <is>
-          <t>LONDA VIÑANZACA NATHALY DANIELA</t>
-        </is>
-      </c>
-      <c r="C66" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D66" s="299" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 9.23 vs Sistema: 9.41)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="25" customHeight="1" s="254">
-      <c r="A67" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B67" s="297" t="inlineStr">
-        <is>
-          <t>LOPEZ DELGADO DANNY LEONEL</t>
-        </is>
-      </c>
-      <c r="C67" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D67" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="25" customHeight="1" s="254">
-      <c r="A68" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B68" s="299" t="inlineStr">
-        <is>
-          <t>MARIN GOMEZ ANDREA BELEN</t>
-        </is>
-      </c>
-      <c r="C68" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D68" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="25" customHeight="1" s="254">
-      <c r="A69" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B69" s="297" t="inlineStr">
-        <is>
-          <t>MOROCHO PELAEZ DANIELA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C69" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D69" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="25" customHeight="1" s="254">
-      <c r="A70" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B70" s="299" t="inlineStr">
-        <is>
-          <t>OVILLO GUALLPA JIMMY XAVIER</t>
-        </is>
-      </c>
-      <c r="C70" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D70" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="25" customHeight="1" s="254">
-      <c r="A71" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B71" s="297" t="inlineStr">
-        <is>
-          <t>PERALTA MENDEZ SAMUEL MATEO</t>
-        </is>
-      </c>
-      <c r="C71" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D71" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="25" customHeight="1" s="254">
-      <c r="A72" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B72" s="299" t="inlineStr">
-        <is>
-          <t>PEÑA ORELLANA MATEO ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C72" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D72" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="25" customHeight="1" s="254">
-      <c r="A73" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B73" s="297" t="inlineStr">
-        <is>
-          <t>PINTADO ROBLES ADELA BELEN</t>
-        </is>
-      </c>
-      <c r="C73" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D73" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="25" customHeight="1" s="254">
-      <c r="A74" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B74" s="299" t="inlineStr">
-        <is>
-          <t>PONCE SANCHEZ NAOMI MADELEIN</t>
-        </is>
-      </c>
-      <c r="C74" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D74" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="25" customHeight="1" s="254">
-      <c r="A75" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B75" s="297" t="inlineStr">
-        <is>
-          <t>QUIZHPE MUÑOZ JHON ESTIVEN</t>
-        </is>
-      </c>
-      <c r="C75" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D75" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="25" customHeight="1" s="254">
-      <c r="A76" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B76" s="299" t="inlineStr">
-        <is>
-          <t>RIVERA GARCIA EMILY MICHELLE</t>
-        </is>
-      </c>
-      <c r="C76" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D76" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="25" customHeight="1" s="254">
-      <c r="A77" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B77" s="297" t="inlineStr">
-        <is>
-          <t>ROMERO ORELLANA AMILIS SOFIA</t>
-        </is>
-      </c>
-      <c r="C77" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D77" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="25" customHeight="1" s="254">
-      <c r="A78" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B78" s="299" t="inlineStr">
-        <is>
-          <t>SARAGURO CARCHIPULLA JOAN ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C78" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D78" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="25" customHeight="1" s="254">
-      <c r="A79" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B79" s="297" t="inlineStr">
-        <is>
-          <t>SOLIZ GUZHÑAY MATEO ISMAEL</t>
-        </is>
-      </c>
-      <c r="C79" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D79" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="25" customHeight="1" s="254">
-      <c r="A80" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B80" s="299" t="inlineStr">
-        <is>
-          <t>SOLIZ GUZHÑAY MATEO ISMAEL</t>
-        </is>
-      </c>
-      <c r="C80" s="298" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D80" s="299" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.4 vs Sistema: 8.43)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="25" customHeight="1" s="254">
-      <c r="A81" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B81" s="297" t="inlineStr">
-        <is>
-          <t>SONGOR LLIVISACA DAYANNA DEL CISNE</t>
-        </is>
-      </c>
-      <c r="C81" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D81" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="25" customHeight="1" s="254">
-      <c r="A82" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B82" s="299" t="inlineStr">
-        <is>
-          <t>TENEZACA JARRIN JEYKING NICOLAS</t>
-        </is>
-      </c>
-      <c r="C82" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D82" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="25" customHeight="1" s="254">
-      <c r="A83" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B83" s="297" t="inlineStr">
-        <is>
-          <t>TOCTE CORRALES JORDY ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C83" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D83" s="297" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="25" customHeight="1" s="254">
-      <c r="A84" s="298" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B84" s="299" t="inlineStr">
-        <is>
-          <t>TORRES SARMIENTO DANIEL MAXIMILIANO</t>
-        </is>
-      </c>
-      <c r="C84" s="298" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D84" s="299" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="25" customHeight="1" s="254">
-      <c r="A85" s="296" t="inlineStr">
-        <is>
-          <t>9BM</t>
-        </is>
-      </c>
-      <c r="B85" s="297" t="inlineStr">
-        <is>
-          <t>VILLAVICENCIO NAVARRO DARWIN ADRIAN</t>
-        </is>
-      </c>
-      <c r="C85" s="296" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D85" s="297" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
+      <c r="C64" s="300" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
+        </is>
+      </c>
+      <c r="D64" s="301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="301" t="inlineStr">
+        <is>
+          <t>Falta</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="22">
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10439,7 +9791,7 @@
       <c r="A40" s="56" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="270" t="inlineStr">
+      <c r="B40" s="287" t="inlineStr">
         <is>
           <t>TOCTE CORRALES SHIRLE LISETH</t>
         </is>
@@ -10483,7 +9835,7 @@
           <t>A+</t>
         </is>
       </c>
-      <c r="N40" s="86">
+      <c r="N40" s="285">
         <f>TRUNC(AVERAGE(D40:J40),2)</f>
         <v/>
       </c>
